--- a/project/data/raw/soybean_oil_2019-2025.xlsx
+++ b/project/data/raw/soybean_oil_2019-2025.xlsx
@@ -956,13 +956,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1217,7 +1210,8 @@
   <sheetFormatPr defaultColWidth="9.90909090909091" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.1818181818182" style="7"/>
-    <col min="2" max="3" width="9" style="8"/>
+    <col min="2" max="2" width="9" style="8"/>
+    <col min="3" max="3" width="11.2727272727273" style="8"/>
     <col min="4" max="5" width="9.55454545454545" style="8"/>
   </cols>
   <sheetData>
@@ -28076,19 +28070,55 @@
         <v>7950</v>
       </c>
     </row>
-    <row r="1560" spans="1:1">
+    <row r="1560" spans="1:5">
       <c r="A1560" s="7">
         <v>45833</v>
       </c>
-    </row>
-    <row r="1561" spans="1:1">
+      <c r="B1560" s="8">
+        <v>7948</v>
+      </c>
+      <c r="C1560" s="8">
+        <v>7988</v>
+      </c>
+      <c r="D1560" s="8">
+        <v>7920</v>
+      </c>
+      <c r="E1560" s="8">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:5">
       <c r="A1561" s="7">
         <v>45834</v>
       </c>
-    </row>
-    <row r="1562" spans="1:1">
+      <c r="B1561" s="8">
+        <v>7956</v>
+      </c>
+      <c r="C1561" s="8">
+        <v>8026</v>
+      </c>
+      <c r="D1561" s="8">
+        <v>7948</v>
+      </c>
+      <c r="E1561" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:5">
       <c r="A1562" s="7">
         <v>45835</v>
+      </c>
+      <c r="B1562" s="8">
+        <v>8012</v>
+      </c>
+      <c r="C1562" s="8">
+        <v>8024</v>
+      </c>
+      <c r="D1562" s="8">
+        <v>7984</v>
+      </c>
+      <c r="E1562" s="8">
+        <v>8002</v>
       </c>
     </row>
   </sheetData>
